--- a/data/trans_dic/P1432-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P1432-Habitat-trans_dic.xlsx
@@ -678,7 +678,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,55; 2,41</t>
+          <t>0,59; 2,36</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -688,37 +688,37 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,35; 1,88</t>
+          <t>0,34; 1,91</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,25; 1,69</t>
+          <t>0,25; 1,68</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>1,23; 3,7</t>
+          <t>1,35; 3,68</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,85; 2,96</t>
+          <t>0,86; 2,99</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,59; 1,77</t>
+          <t>0,56; 1,64</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,75; 2,1</t>
+          <t>0,79; 2,13</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,75; 1,92</t>
+          <t>0,77; 2,08</t>
         </is>
       </c>
     </row>
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,52; 1,9</t>
+          <t>0,53; 1,83</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,21; 1,59</t>
+          <t>0,21; 1,66</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,18; 1,06</t>
+          <t>0,18; 1,15</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1,01; 2,81</t>
+          <t>0,99; 2,89</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,86; 2,36</t>
+          <t>0,85; 2,4</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,56; 1,91</t>
+          <t>0,57; 1,96</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,92; 2,06</t>
+          <t>0,91; 2,05</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,69; 1,7</t>
+          <t>0,66; 1,76</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,47; 1,29</t>
+          <t>0,5; 1,3</t>
         </is>
       </c>
     </row>
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,39; 2,1</t>
+          <t>0,48; 2,18</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,28; 1,67</t>
+          <t>0,39; 1,77</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,13; 1,21</t>
+          <t>0,12; 1,24</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,88; 2,85</t>
+          <t>0,85; 2,76</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,77; 2,8</t>
+          <t>0,8; 2,87</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,9; 2,93</t>
+          <t>0,91; 2,86</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,8; 2,08</t>
+          <t>0,78; 2,07</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,67; 1,92</t>
+          <t>0,65; 1,87</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,62; 1,73</t>
+          <t>0,64; 1,76</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,53; 1,74</t>
+          <t>0,53; 1,68</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,32; 1,72</t>
+          <t>0,32; 1,79</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,08; 0,69</t>
+          <t>0,08; 0,77</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1,05; 2,7</t>
+          <t>1,0; 2,63</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,85; 2,3</t>
+          <t>0,86; 2,3</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,79; 2,49</t>
+          <t>0,74; 2,57</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,93; 1,96</t>
+          <t>0,91; 1,99</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,76; 1,77</t>
+          <t>0,71; 1,67</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,54; 1,53</t>
+          <t>0,52; 1,4</t>
         </is>
       </c>
     </row>
@@ -1118,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,81; 1,51</t>
+          <t>0,8; 1,52</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,4; 1,01</t>
+          <t>0,42; 1,05</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,31; 0,77</t>
+          <t>0,31; 0,82</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1,13; 2,01</t>
+          <t>1,11; 1,96</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>1,21; 2,12</t>
+          <t>1,23; 2,08</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,09; 1,96</t>
+          <t>0,99; 1,9</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,04; 1,6</t>
+          <t>1,03; 1,61</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,92; 1,45</t>
+          <t>0,89; 1,44</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,78; 1,26</t>
+          <t>0,78; 1,28</t>
         </is>
       </c>
     </row>
@@ -1417,47 +1417,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>3825; 16693</t>
+          <t>4085; 16396</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0; 7071</t>
+          <t>0; 7086</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>2395; 12670</t>
+          <t>2310; 12864</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>1709; 11623</t>
+          <t>1712; 11541</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>8607; 25787</t>
+          <t>9423; 25683</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>5714; 19908</t>
+          <t>5801; 20149</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>8106; 24456</t>
+          <t>7810; 22684</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>10498; 29455</t>
+          <t>11080; 29887</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>10121; 25808</t>
+          <t>10380; 28003</t>
         </is>
       </c>
     </row>
@@ -1580,47 +1580,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>5034; 18261</t>
+          <t>5129; 17554</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2128; 16135</t>
+          <t>2135; 16900</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1829; 10886</t>
+          <t>1810; 11779</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>9746; 27242</t>
+          <t>9587; 28015</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>8857; 24272</t>
+          <t>8776; 24664</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>5837; 19896</t>
+          <t>5921; 20465</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>17830; 39763</t>
+          <t>17546; 39570</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>14070; 34801</t>
+          <t>13566; 35996</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>9625; 26607</t>
+          <t>10246; 26890</t>
         </is>
       </c>
     </row>
@@ -1743,47 +1743,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>2679; 14279</t>
+          <t>3240; 14764</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>2089; 12678</t>
+          <t>2983; 13389</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1013; 9194</t>
+          <t>904; 9438</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>6029; 19491</t>
+          <t>5827; 18863</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>6005; 21769</t>
+          <t>6186; 22304</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>7064; 23029</t>
+          <t>7105; 22466</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>10898; 28283</t>
+          <t>10669; 28165</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>10307; 29417</t>
+          <t>10015; 28616</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>9638; 26796</t>
+          <t>9866; 27134</t>
         </is>
       </c>
     </row>
@@ -1906,47 +1906,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>5031; 16410</t>
+          <t>4949; 15838</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>3017; 16294</t>
+          <t>3025; 17002</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>773; 6424</t>
+          <t>784; 7186</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>10854; 28003</t>
+          <t>10372; 27301</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>8960; 24212</t>
+          <t>9002; 24197</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>8270; 26000</t>
+          <t>7737; 26874</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>18389; 38739</t>
+          <t>17958; 39468</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>15107; 35470</t>
+          <t>14168; 33487</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>10781; 30253</t>
+          <t>10253; 27825</t>
         </is>
       </c>
     </row>
@@ -2069,47 +2069,47 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>26480; 49392</t>
+          <t>26081; 49788</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>13565; 34740</t>
+          <t>14263; 35835</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>10591; 26279</t>
+          <t>10477; 27785</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>38308; 68044</t>
+          <t>37609; 66395</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>43029; 75272</t>
+          <t>43559; 73835</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>38462; 69353</t>
+          <t>35140; 67268</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>68992; 106354</t>
+          <t>68472; 106966</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>64090; 101372</t>
+          <t>62191; 100231</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>53794; 87626</t>
+          <t>54011; 88710</t>
         </is>
       </c>
     </row>
